--- a/doe_2026-10-12.xlsx
+++ b/doe_2026-10-12.xlsx
@@ -3343,7 +3343,7 @@
         <v>내보낸 시각</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-12T23:04:49</v>
+        <v>2026-10-12T23:11:47</v>
       </c>
     </row>
     <row r="3">
